--- a/data/trans_bre/IQ2606_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IQ2606_R2-Provincia-trans_bre.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-20,26%</t>
+          <t>-20,7%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 11,83</t>
+          <t>-17,71; 11,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 20,55</t>
+          <t>-3,99; 20,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-40,93; 13,6</t>
+          <t>-45,39; 11,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 19,45</t>
+          <t>-23,25; 18,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 30,75</t>
+          <t>-4,77; 31,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,63; 21,97</t>
+          <t>-54,25; 17,72</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,35</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 11,55</t>
+          <t>-8,36; 11,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 5,49</t>
+          <t>-7,69; 5,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 15,96</t>
+          <t>-17,16; 18,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 15,49</t>
+          <t>-9,72; 15,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 6,26</t>
+          <t>-8,16; 6,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 19,99</t>
+          <t>-18,71; 24,41</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,2</t>
+          <t>8,61</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 30,82</t>
+          <t>1,37; 29,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 10,82</t>
+          <t>-16,31; 11,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 32,37</t>
+          <t>-13,41; 31,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 75,26</t>
+          <t>1,74; 66,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-34,81; 29,82</t>
+          <t>-32,34; 31,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 58,37</t>
+          <t>-15,93; 58,24</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-26,23</t>
+          <t>-25,93</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-26,23%</t>
+          <t>-25,93%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 11,43</t>
+          <t>-15,8; 10,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 5,02</t>
+          <t>-17,95; 4,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,58; -8,81</t>
+          <t>-52,53; -7,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,15; 31,39</t>
+          <t>-29,96; 26,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 6,53</t>
+          <t>-21,66; 6,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,58; -8,81</t>
+          <t>-52,53; -7,64</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-8,19</t>
+          <t>-6,97</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,13%</t>
+          <t>-7,83%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 25,09</t>
+          <t>-8,86; 25,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 28,19</t>
+          <t>-4,04; 30,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 14,47</t>
+          <t>-29,92; 13,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 56,27</t>
+          <t>-14,56; 51,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 62,34</t>
+          <t>-5,68; 66,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,25; 17,56</t>
+          <t>-32,41; 17,44</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6,48</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 17,99</t>
+          <t>-14,85; 16,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 6,87</t>
+          <t>-16,01; 6,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 29,34</t>
+          <t>-25,63; 31,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 47,21</t>
+          <t>-25,04; 42,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 8,52</t>
+          <t>-17,68; 8,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 48,09</t>
+          <t>-30,37; 49,93</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>0,05%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 17,03</t>
+          <t>-3,12; 16,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 13,06</t>
+          <t>-5,06; 13,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 15,28</t>
+          <t>-12,9; 14,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 39,24</t>
+          <t>-5,95; 38,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 20,85</t>
+          <t>-6,93; 20,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 19,07</t>
+          <t>-13,59; 17,46</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 14,57</t>
+          <t>-2,25; 15,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 2,76</t>
+          <t>-12,03; 2,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 11,82</t>
+          <t>-12,08; 10,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 26,57</t>
+          <t>-3,46; 26,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 3,74</t>
+          <t>-15,14; 3,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 13,78</t>
+          <t>-12,76; 12,38</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,36%</t>
+          <t>-3,42%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 8,91</t>
+          <t>0,1; 8,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 3,67</t>
+          <t>-3,85; 3,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 4,45</t>
+          <t>-9,98; 3,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 16,07</t>
+          <t>0,27; 15,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 5,13</t>
+          <t>-5,16; 4,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 5,39</t>
+          <t>-11,35; 4,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2606_R2-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IQ2606_R2-Provincia-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,7 +529,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más, siempre o casi siempre</t>
+          <t>Menores que el verano pasado emplearon crema solar con factor de protección de 50 o más, siempre o casi siempre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,03</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,02</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-15,38</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,01%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-20,7%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.026839254378987</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>8.018141854936289</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-15.38112982828278</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.03007850397406352</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1095060657550313</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.2070061656409988</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-17,71; 11,66</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,99; 20,52</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-45,39; 11,42</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-23,25; 18,91</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-4,77; 31,81</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-54,25; 17,72</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-17.71045769288905</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.98812817103832</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-45.39159431656664</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.2324701447241741</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.04769429769248223</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5424713205814483</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.66058169942025</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>20.52443709095027</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>11.41594299213572</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.189139850239478</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.3181038896297545</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1771802181523355</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Cádiz</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,44</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-1,07%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,36; 11,07</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,69; 5,75</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-17,16; 18,53</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-9,72; 15,25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-8,16; 6,5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-18,71; 24,41</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.441576915403031</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.9728429915605852</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.780294105845214</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.01836693633574442</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.01069350298716153</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.009059016024132102</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>15,48</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,8</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8,61</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31,51%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-6,29%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,06%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.356938098082733</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.688066933962717</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-17.16088741107318</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.09718538120871524</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.08157814306030819</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1870506138996052</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 29,32</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-16,31; 11,62</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-13,41; 31,37</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,74; 66,45</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-32,34; 31,25</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-15,93; 58,24</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>11.07497910706462</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.75225354116267</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>18.53394700722141</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.1524737041270418</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.06500614255084834</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2441335802388898</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +767,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,46</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-6,88</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-25,93</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-5,3%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-8,6%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-25,93%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>15.48000548758595</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.803692462295754</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>8.608568560547702</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.3150941569401787</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.06286366416831853</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.1205821382691194</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-15,8; 10,61</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-17,95; 4,55</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-52,53; -7,64</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-29,96; 26,88</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-21,66; 6,14</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-52,53; -7,64</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.372494381320433</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-16.30560412169234</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-13.40714559755478</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0.01738958989687247</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.3234287864687332</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1592599396050147</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Huelva</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>29.31934546456157</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.61678488030379</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>31.36601932767499</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.6644872548454698</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.3125315506676911</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.5823658914003552</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,93</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>12,22</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-6,97</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14,14%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-7,83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-8,86; 25,38</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,04; 30,09</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-29,92; 13,86</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-14,56; 51,68</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-5,68; 66,4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-32,41; 17,44</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-2.459264549876905</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-6.881309802537627</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-25.93083149788558</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.05304709430328507</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.08598372819791393</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2593083149788558</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Jaén</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-4,08</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5,53</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-4,81%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-15.80238907405344</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-17.94674920894334</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-52.525567943086</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.2995821158229109</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2165730565032253</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.52525567943086</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-14,85; 16,71</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-16,01; 6,98</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-25,63; 31,09</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-25,04; 42,1</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-17,68; 8,82</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-30,37; 49,93</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>10.60986168355047</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.553825694506928</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-7.636096285592712</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.2687872047773478</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.06141681030987478</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.07636096285592713</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,237 +931,407 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>6,55</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3,74</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13,65%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>7.926927388454985</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>12.22418751347152</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-6.972140655623605</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.1414036796955002</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.2190262554695055</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.07829764110770318</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-3,12; 16,51</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-5,06; 13,04</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-12,9; 14,44</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-5,95; 38,36</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-6,93; 20,45</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-13,59; 17,46</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-8.86311224333858</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.036936576132788</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-29.91605854796102</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.1455517420430122</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.05677634744182778</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3241363226821923</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>25.37642227184288</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>30.09493948390112</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>13.864078316611</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.5167503541151643</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.6640227018795143</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.174444571660794</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>6,05</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-4,6</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-6,05%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-2,25; 15,12</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-12,03; 2,91</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-12,08; 10,59</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-3,46; 26,37</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-15,14; 3,97</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-12,76; 12,38</t>
-        </is>
+      <c r="C19" s="5" t="n">
+        <v>1.092025036631583</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-4.081501677227905</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>5.527745331965662</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.0218269489118202</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.04811012053848442</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.07506655923595232</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>4,55</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,93</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,46%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-3,42%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-14.84579644680985</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-16.00611135629462</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-25.63384414514606</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.2504143810747734</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.1767901529320696</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.303677148700619</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 8,53</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-3,85; 3,52</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-9,98; 3,72</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0,27; 15,37</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>-5,16; 4,93</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-11,35; 4,58</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>16.70713511706287</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>6.976540513352575</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>31.09037276493434</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.4210154150850423</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.0881771546873279</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.4993029487160691</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>6.550834303642977</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3.744443890382343</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.04791737375439142</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.1365055826016954</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.05515226238189334</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.0005358909680689982</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-3.117423220566407</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-5.061192948330211</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-12.89530960825389</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-0.05946438929012759</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.06928684601878454</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.1359216006627738</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>16.51310795847873</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>13.04173927662621</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>14.44141736562567</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.3835930664230319</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.2045156978843379</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.1746303585023419</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>6.045695422490393</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-4.602158046700811</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.7765678679182098</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.09972899791755267</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.06048654061019378</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.00847025413877096</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-2.252966927194539</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-12.03090147102156</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-12.0758858840102</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.03460718783049777</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.1514167376464507</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.1275812514919307</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>15.12282067456275</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>2.912180162299516</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>10.58727699540781</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.2636639951018372</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.03973934302931192</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.1238000427227035</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>4.547836484341872</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-0.3351055993549013</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-2.929035505774136</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0.07899652103885399</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>-0.004566435591841512</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>-0.03418950440371978</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0.1008196889340038</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-3.854760058914387</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-9.980223839079811</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0.002726308143434902</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-0.05163330710970351</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>-0.1135236177208179</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>8.534949840903913</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.520854276043286</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>3.723646708124626</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>0.1537358137930534</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0.04932372641546322</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>0.0458041531729814</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1313,17 +1340,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
